--- a/Excel/Dulieukhongnguoi.xlsx
+++ b/Excel/Dulieukhongnguoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_Tu_Dong_PPTX_New\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0035CF-84E8-4215-A19C-F6CB161C258E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9128CBB-8AF1-43B2-A295-971052B1A84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-1584" windowWidth="23256" windowHeight="13896" xr2:uid="{BDE846C5-E219-4DBF-9831-BDDBF6BB9F56}"/>
   </bookViews>
@@ -4025,7 +4025,9 @@
       <c r="N15" s="9">
         <v>39055</v>
       </c>
-      <c r="O15" s="9"/>
+      <c r="O15" s="9">
+        <v>35750</v>
+      </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -4076,7 +4078,9 @@
       <c r="N16" s="9">
         <v>4605</v>
       </c>
-      <c r="O16" s="9"/>
+      <c r="O16" s="9">
+        <v>6293</v>
+      </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -4127,7 +4131,9 @@
       <c r="N17" s="9">
         <v>1500</v>
       </c>
-      <c r="O17" s="9"/>
+      <c r="O17" s="9">
+        <v>316</v>
+      </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -4178,7 +4184,9 @@
       <c r="N18" s="9">
         <v>2500</v>
       </c>
-      <c r="O18" s="9"/>
+      <c r="O18" s="9">
+        <v>723</v>
+      </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -4230,9 +4238,9 @@
         <f>IFERROR(N16/N$15*100,"")</f>
         <v>11.791063884265778</v>
       </c>
-      <c r="O19" s="10" t="str">
+      <c r="O19" s="10">
         <f t="shared" ref="O19:AS21" si="3">IFERROR(O16/O$15*100,"")</f>
-        <v/>
+        <v>17.602797202797202</v>
       </c>
       <c r="P19" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4375,9 +4383,9 @@
         <f t="shared" ref="N20:AC21" si="4">IFERROR(N17/N$15*100,"")</f>
         <v>3.8407374215849446</v>
       </c>
-      <c r="O20" s="10" t="str">
+      <c r="O20" s="10">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.88391608391608389</v>
       </c>
       <c r="P20" s="10" t="str">
         <f t="shared" si="4"/>
@@ -4520,9 +4528,9 @@
         <f t="shared" si="4"/>
         <v>6.4012290359749073</v>
       </c>
-      <c r="O21" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="O21" s="10">
+        <f t="shared" si="3"/>
+        <v>2.0223776223776224</v>
       </c>
       <c r="P21" s="10" t="str">
         <f t="shared" si="3"/>
